--- a/MapData/Map1.xlsx
+++ b/MapData/Map1.xlsx
@@ -8,17 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student3\source\repos\DX_GAME\MapData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8829B16E-7505-40B8-BF59-F2B5A46C445A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{833D437F-C758-476B-8F22-13A11B45ECCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="1620" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="672" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Main" sheetId="6" r:id="rId1"/>
+    <sheet name="コマンド" sheetId="1" r:id="rId2"/>
+    <sheet name="Flag" sheetId="3" r:id="rId3"/>
+    <sheet name="Type" sheetId="4" r:id="rId4"/>
+    <sheet name="TilePos.X" sheetId="5" r:id="rId5"/>
+    <sheet name="TilePos.Y" sheetId="7" r:id="rId6"/>
+    <sheet name="TilePos.Z" sheetId="8" r:id="rId7"/>
+    <sheet name="Adjacent" sheetId="9" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -27,8 +43,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="20">
   <si>
     <t>flag</t>
     <phoneticPr fontId="1"/>
@@ -84,12 +122,33 @@
     <t>隣接7</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>列1</t>
+  </si>
+  <si>
+    <t>列2</t>
+  </si>
+  <si>
+    <t>列3</t>
+  </si>
+  <si>
+    <t>列4</t>
+  </si>
+  <si>
+    <t>列5</t>
+  </si>
+  <si>
+    <t>列6</t>
+  </si>
+  <si>
+    <t>列7</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,6 +171,12 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -133,14 +198,46 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -151,6 +248,121 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{3ED57A74-A917-4CC0-A492-FEEEFFAE20F2}" name="テーブル6" displayName="テーブル6" ref="A1:G17" headerRowCount="0" totalsRowShown="0">
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{50C27DF0-A62B-4045-AFB9-14BD8A1E5F21}" name="列1" dataDxfId="3">
+      <calculatedColumnFormula array="1">INDIRECT("コマンド!H"&amp;ROW(A1))&amp;""</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{A0F85972-614D-475D-8FF3-B5A16E93EA92}" name="列2"/>
+    <tableColumn id="3" xr3:uid="{803BBCC1-DAAB-4C74-94F2-AF1D39DC25B2}" name="列3"/>
+    <tableColumn id="4" xr3:uid="{EF77421D-F8BB-4CFA-A722-25F873B138C7}" name="列4"/>
+    <tableColumn id="5" xr3:uid="{5D594EFF-D797-4604-AF02-9879CA54AA12}" name="列5"/>
+    <tableColumn id="6" xr3:uid="{69E26970-EC5A-485B-BFF8-3D9F417A5656}" name="列6"/>
+    <tableColumn id="7" xr3:uid="{33B81854-555C-45E5-964A-107F07083000}" name="列7"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DF2C319E-0FDC-485B-A442-B589E405C222}" name="テーブル1" displayName="テーブル1" ref="A2:G9" totalsRowShown="0">
+  <autoFilter ref="A2:G9" xr:uid="{DF2C319E-0FDC-485B-A442-B589E405C222}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{F1014F82-3E85-46F0-ADBA-C85C00C8ED71}" name="列1"/>
+    <tableColumn id="2" xr3:uid="{0D5BD3E9-6B63-4B95-885F-44B73A647180}" name="列2"/>
+    <tableColumn id="3" xr3:uid="{39722661-2C26-4602-890B-00E4C74B6787}" name="列3"/>
+    <tableColumn id="4" xr3:uid="{C3B833B1-EC58-449F-8A78-C46020A73B10}" name="列4"/>
+    <tableColumn id="5" xr3:uid="{9A78DAF7-74DB-482A-BDFC-F85ABDF15598}" name="列5"/>
+    <tableColumn id="6" xr3:uid="{B8E92118-5FCD-42FB-B22F-5EB36A3255E5}" name="列6"/>
+    <tableColumn id="7" xr3:uid="{22E9C389-8B28-4449-AFEE-BA004CB6A23D}" name="列7"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F235384E-981E-4F94-BD0B-07FF4E1037BD}" name="テーブル2" displayName="テーブル2" ref="A10:G17" totalsRowShown="0">
+  <autoFilter ref="A10:G17" xr:uid="{F235384E-981E-4F94-BD0B-07FF4E1037BD}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{0DEB9DC2-D7DC-463F-8AD0-7353B2133A2B}" name="列1"/>
+    <tableColumn id="2" xr3:uid="{E8E26413-8CAA-4075-821C-08B7E8AF367B}" name="列2"/>
+    <tableColumn id="3" xr3:uid="{92B58E6D-A91A-4083-B900-BA7C82EFA02A}" name="列3"/>
+    <tableColumn id="4" xr3:uid="{3E392A83-2705-4399-A029-4A1BE88B677C}" name="列4"/>
+    <tableColumn id="5" xr3:uid="{73FE2F02-76D9-4464-92B3-940F76307343}" name="列5"/>
+    <tableColumn id="6" xr3:uid="{C3C0B170-F16A-41DC-936C-FCD325013EF5}" name="列6"/>
+    <tableColumn id="7" xr3:uid="{14549EB1-6640-4A60-B591-DDB790BF229D}" name="列7"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{83137655-8A87-499C-8B16-1803EF70A12B}" name="テーブル3" displayName="テーブル3" ref="A18:G25" totalsRowShown="0">
+  <autoFilter ref="A18:G25" xr:uid="{83137655-8A87-499C-8B16-1803EF70A12B}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{B71F11AF-24D3-437B-AF12-F3517C646A9E}" name="列1"/>
+    <tableColumn id="2" xr3:uid="{A1D310E5-4A5A-4EBA-8185-C345EE5E2C03}" name="列2"/>
+    <tableColumn id="3" xr3:uid="{E99E5A1D-1939-4566-9B77-660FB766DD18}" name="列3"/>
+    <tableColumn id="4" xr3:uid="{2FAD7B68-D198-475A-86D8-F4367008BAEB}" name="列4"/>
+    <tableColumn id="5" xr3:uid="{E4EF63B6-490F-49C2-8A33-5300E9BB47B8}" name="列5"/>
+    <tableColumn id="6" xr3:uid="{911B2AF8-9754-40A8-A48F-F2FEA2152C25}" name="列6"/>
+    <tableColumn id="7" xr3:uid="{13C20E99-7696-40EE-A2E1-9FB743B5D6E0}" name="列7"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{BD81F3DB-1C6C-48F3-82EE-A7B4CAEF217E}" name="テーブル4" displayName="テーブル4" ref="A26:G33" totalsRowShown="0">
+  <autoFilter ref="A26:G33" xr:uid="{BD81F3DB-1C6C-48F3-82EE-A7B4CAEF217E}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{3C0EDCCF-4C89-42D2-A398-89796240CDFD}" name="列1"/>
+    <tableColumn id="2" xr3:uid="{813E6423-CB78-4255-B8F2-6CD3277D240F}" name="列2"/>
+    <tableColumn id="3" xr3:uid="{F885EF57-E8CD-46D3-9866-D968A24352C2}" name="列3"/>
+    <tableColumn id="4" xr3:uid="{F0312346-065A-414F-B2BE-E545A8632B5C}" name="列4"/>
+    <tableColumn id="5" xr3:uid="{3173FE43-7352-4A42-B38A-C1DC3CE6993E}" name="列5"/>
+    <tableColumn id="6" xr3:uid="{93AC98E6-6E43-410F-A855-5C0CF9982805}" name="列6"/>
+    <tableColumn id="7" xr3:uid="{6EF25C55-63AE-4558-B6E0-F8C6E222D07E}" name="列7"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{86F42E63-7697-4B7B-8940-1ABB8C968DF9}" name="テーブル7" displayName="テーブル7" ref="H1:N10" headerRowCount="0" totalsRowShown="0">
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{19B6EECF-4661-4D6F-B27B-B0C0B5A532F7}" name="列1" headerRowDxfId="2" dataDxfId="1">
+      <calculatedColumnFormula array="1">INDIRECT("A"&amp;ROW(A1))&amp;""</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{A6513A46-AAF1-4C21-837A-B0065214A24B}" name="列2"/>
+    <tableColumn id="3" xr3:uid="{DB4A90FC-C9E4-4FB9-BCB5-BC9CDD51B3B2}" name="列3"/>
+    <tableColumn id="4" xr3:uid="{4387F852-5750-459F-B51A-D667223A68FF}" name="列4"/>
+    <tableColumn id="5" xr3:uid="{24E61415-EFAE-42CE-9E2C-B46D2532929A}" name="列5"/>
+    <tableColumn id="6" xr3:uid="{3BAD5DCA-199C-478A-8057-6D4278FB70DF}" name="列6"/>
+    <tableColumn id="7" xr3:uid="{05246261-1844-4866-8CA0-7C15A8C1768C}" name="列7"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{7567D4AA-8869-480A-A875-D3D1FB6B856C}" name="テーブル8" displayName="テーブル8" ref="H12:N23" headerRowCount="0" totalsRowShown="0">
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{AC7BC3E3-8042-4B42-A952-9CCDDC59D68C}" name="列1" dataDxfId="0">
+      <calculatedColumnFormula array="1">INDIRECT("A"&amp;ROW(A1))&amp;""</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{BB9BDD53-ED5A-43CC-959B-ED72A0098864}" name="列2"/>
+    <tableColumn id="3" xr3:uid="{CF17698C-4C16-463E-980F-8C873891D84C}" name="列3"/>
+    <tableColumn id="4" xr3:uid="{615F1EEC-C9F8-4C30-8ED3-FAB26A0AA15A}" name="列4"/>
+    <tableColumn id="5" xr3:uid="{8755B5F4-285C-49B5-AD27-6CBC5CD12E64}" name="列5"/>
+    <tableColumn id="6" xr3:uid="{25C96000-8900-4FA0-A69A-8C328BD980E2}" name="列6"/>
+    <tableColumn id="7" xr3:uid="{DCB1661E-FED6-4A4B-94BB-6906711192E9}" name="列7"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -415,136 +627,477 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B85"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49DE0A64-7783-4824-A25C-9B4F0765F26D}">
+  <dimension ref="A1:A17"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">INDIRECT("コマンド!H"&amp;ROW(A1))&amp;""</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="str" cm="1">
+        <f t="array" aca="1" ref="A2" ca="1">INDIRECT("コマンド!H"&amp;ROW(A2))&amp;""</f>
+        <v>列1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="str" cm="1">
+        <f t="array" aca="1" ref="A3" ca="1">INDIRECT("コマンド!H"&amp;ROW(A3))&amp;""</f>
+        <v>flag</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="str" cm="1">
+        <f t="array" aca="1" ref="A4" ca="1">INDIRECT("コマンド!H"&amp;ROW(A4))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="str" cm="1">
+        <f t="array" aca="1" ref="A5" ca="1">INDIRECT("コマンド!H"&amp;ROW(A5))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="str" cm="1">
+        <f t="array" aca="1" ref="A6" ca="1">INDIRECT("コマンド!H"&amp;ROW(A6))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="str" cm="1">
+        <f t="array" aca="1" ref="A7" ca="1">INDIRECT("コマンド!H"&amp;ROW(A7))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="str" cm="1">
+        <f t="array" aca="1" ref="A8" ca="1">INDIRECT("コマンド!H"&amp;ROW(A8))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="str" cm="1">
+        <f t="array" aca="1" ref="A9" ca="1">INDIRECT("コマンド!H"&amp;ROW(A9))&amp;""</f>
+        <v>flag</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="str" cm="1">
+        <f t="array" aca="1" ref="A10" ca="1">INDIRECT("コマンド!H"&amp;ROW(A10))&amp;""</f>
+        <v>列1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="str" cm="1">
+        <f t="array" aca="1" ref="A11" ca="1">INDIRECT("コマンド!H"&amp;ROW(A11))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="str" cm="1">
+        <f t="array" aca="1" ref="A12" ca="1">INDIRECT("コマンド!H"&amp;ROW(A12))&amp;""</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="str" cm="1">
+        <f t="array" aca="1" ref="A13" ca="1">INDIRECT("コマンド!H"&amp;ROW(A13))&amp;""</f>
+        <v>列1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="str" cm="1">
+        <f t="array" aca="1" ref="A14" ca="1">INDIRECT("コマンド!H"&amp;ROW(A14))&amp;""</f>
+        <v>flag</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="str" cm="1">
+        <f t="array" aca="1" ref="A15" ca="1">INDIRECT("コマンド!H"&amp;ROW(A15))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="str" cm="1">
+        <f t="array" aca="1" ref="A16" ca="1">INDIRECT("コマンド!H"&amp;ROW(A16))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="str" cm="1">
+        <f t="array" aca="1" ref="A17" ca="1">INDIRECT("コマンド!H"&amp;ROW(A17))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H89"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:8">
       <c r="A1">
         <v>7</v>
       </c>
       <c r="B1">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="H1" s="2" t="str" cm="1">
+        <f t="array" aca="1" ref="H1" ca="1">INDIRECT("A"&amp;ROW(A1))&amp;""</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="19.5" customHeight="1">
       <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="str" cm="1">
+        <f t="array" aca="1" ref="H2" ca="1">INDIRECT("A"&amp;ROW(A2))&amp;""</f>
+        <v>列1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
+      <c r="H3" t="str" cm="1">
+        <f t="array" aca="1" ref="H3" ca="1">INDIRECT("A"&amp;ROW(A3))&amp;""</f>
+        <v>flag</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="H4" t="str" cm="1">
+        <f t="array" aca="1" ref="H4" ca="1">INDIRECT("A"&amp;ROW(A4))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="H5" t="str" cm="1">
+        <f t="array" aca="1" ref="H5" ca="1">INDIRECT("A"&amp;ROW(A5))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="H6" t="str" cm="1">
+        <f t="array" aca="1" ref="H6" ca="1">INDIRECT("A"&amp;ROW(A6))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="H7" t="str" cm="1">
+        <f t="array" aca="1" ref="H7" ca="1">INDIRECT("A"&amp;ROW(A7))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="H8" t="str" cm="1">
+        <f t="array" aca="1" ref="H8" ca="1">INDIRECT("A"&amp;ROW(A8))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
+      <c r="H9" t="str" cm="1">
+        <f t="array" aca="1" ref="H9" ca="1">INDIRECT("A"&amp;ROW(A9))&amp;""</f>
+        <v>flag</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" t="str" cm="1">
+        <f t="array" aca="1" ref="H10" ca="1">INDIRECT("A"&amp;ROW(A10))&amp;""</f>
+        <v>列1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
+    <row r="12" spans="1:8">
+      <c r="H12" t="str" cm="1">
+        <f t="array" aca="1" ref="H12" ca="1">INDIRECT("A"&amp;ROW(A1))&amp;""</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="H13" t="str" cm="1">
+        <f t="array" aca="1" ref="H13" ca="1">INDIRECT("A"&amp;ROW(A2))&amp;""</f>
+        <v>列1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="H14" t="str" cm="1">
+        <f t="array" aca="1" ref="H14" ca="1">INDIRECT("A"&amp;ROW(A3))&amp;""</f>
+        <v>flag</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="H15" t="str" cm="1">
+        <f t="array" aca="1" ref="H15" ca="1">INDIRECT("A"&amp;ROW(A4))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="H16" t="str" cm="1">
+        <f t="array" aca="1" ref="H16" ca="1">INDIRECT("A"&amp;ROW(A5))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
+      <c r="H17" t="str" cm="1">
+        <f t="array" aca="1" ref="H17" ca="1">INDIRECT("A"&amp;ROW(A6))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" t="str" cm="1">
+        <f t="array" aca="1" ref="H18" ca="1">INDIRECT("A"&amp;ROW(A7))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
+      <c r="H19" t="str" cm="1">
+        <f t="array" aca="1" ref="H19" ca="1">INDIRECT("A"&amp;ROW(A8))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="H20" t="str" cm="1">
+        <f t="array" aca="1" ref="H20" ca="1">INDIRECT("A"&amp;ROW(A9))&amp;""</f>
+        <v>flag</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="H21" t="str" cm="1">
+        <f t="array" aca="1" ref="H21" ca="1">INDIRECT("A"&amp;ROW(A10))&amp;""</f>
+        <v>列1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="H22" t="str" cm="1">
+        <f t="array" aca="1" ref="H22" ca="1">INDIRECT("A"&amp;ROW(A11))&amp;""</f>
+        <v>type</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="H23" t="str" cm="1">
+        <f t="array" aca="1" ref="H23" ca="1">INDIRECT("A"&amp;ROW(A12))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:1" s="1" customFormat="1"/>
-    <row r="36" spans="1:1">
-      <c r="A36" t="s">
+    <row r="35" spans="1:7" s="1" customFormat="1">
+      <c r="A35"/>
+      <c r="B35"/>
+      <c r="C35"/>
+      <c r="D35"/>
+      <c r="E35"/>
+      <c r="F35"/>
+      <c r="G35"/>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
+    <row r="41" spans="1:7">
+      <c r="A41" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
+    <row r="47" spans="1:7">
+      <c r="A47" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
+    <row r="48" spans="1:7">
+      <c r="A48" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
-      <c r="A58" t="s">
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
-      <c r="A64" t="s">
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
-      <c r="A65" t="s">
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:1">
-      <c r="A71" t="s">
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:1">
-      <c r="A72" t="s">
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:1">
-      <c r="A78" t="s">
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="79" spans="1:1">
-      <c r="A79" t="s">
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="85" spans="1:1">
-      <c r="A85" t="s">
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
         <v>12</v>
       </c>
     </row>
@@ -552,5 +1105,73 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <tableParts count="6">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
+    <tablePart r:id="rId7"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE23C999-0255-4055-BC8C-FC7618EF5381}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4CEDB1D-FDA7-4277-A343-CBF4C8DBC1E2}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46CFA1CB-56F9-4AD5-B153-6AD4B50CC3CC}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9D9D6B4-216F-4EB6-BD8C-E4C6683FD25D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39122337-C3D3-4AF4-86F1-926914215784}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C804C5CB-F9CD-4C46-A2BB-701C304ED0B1}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/MapData/Map1.xlsx
+++ b/MapData/Map1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student3\source\repos\DX_GAME\MapData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{833D437F-C758-476B-8F22-13A11B45ECCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6467D270-F29B-4B6F-9604-CB162C470792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="672" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1173,5 +1173,6 @@
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/MapData/Map1.xlsx
+++ b/MapData/Map1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student3\source\repos\DX_GAME\MapData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6467D270-F29B-4B6F-9604-CB162C470792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F603397-684A-429A-87B0-1453B69640B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="672" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="-2910" yWindow="3570" windowWidth="21600" windowHeight="8310" tabRatio="672" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="6" r:id="rId1"/>
